--- a/tables/StageLayer.xlsx
+++ b/tables/StageLayer.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.13" customWidth="1" min="1" max="1"/>
@@ -585,11 +585,6 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
@@ -627,11 +622,6 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
           <t>불타는 밤하늘</t>
         </is>
       </c>
@@ -669,11 +659,6 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
           <t>산자락</t>
         </is>
       </c>
@@ -711,11 +696,6 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
           <t>불타는 초가</t>
         </is>
       </c>
@@ -753,11 +733,6 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
           <t>밟는 땅</t>
         </is>
       </c>
@@ -795,11 +770,6 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
           <t>연기·불티</t>
         </is>
       </c>
@@ -835,11 +805,6 @@
       <c r="H12" s="3" t="n">
         <v>-40</v>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -872,11 +837,6 @@
       <c r="H13" s="3" t="n">
         <v>-30</v>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -909,11 +869,6 @@
       <c r="H14" s="3" t="n">
         <v>-20</v>
       </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -946,11 +901,6 @@
       <c r="H15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -983,11 +933,6 @@
       <c r="H16" s="3" t="n">
         <v>-40</v>
       </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1020,11 +965,6 @@
       <c r="H17" s="3" t="n">
         <v>-30</v>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1057,11 +997,6 @@
       <c r="H18" s="3" t="n">
         <v>-20</v>
       </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1094,11 +1029,6 @@
       <c r="H19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1133,11 +1063,6 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
           <t>보스방은 고정 화면에 가까움</t>
         </is>
       </c>
@@ -1172,11 +1097,6 @@
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/tables/StageLayer.xlsx
+++ b/tables/StageLayer.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>레이어 순서·이미지·패럴랙스·정렬.</t>
+          <t>CSV,레이어 순서·이미지·패럴랙스·정렬.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>

--- a/tables/StageLayer.xlsx
+++ b/tables/StageLayer.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 스테이지의 배경 레이어 하나. StageID는 Stage ID. Parallax는 카메라 이동 대비 만분율(0=고정, 10000=플레이 레이어와 같이).</t>
+          <t>한 행 = 스테이지의 배경 레이어 하나. StageID는 Stage ID. Parallax는 카메라 이동 대비 만분율(0=고정, 10000=플레이 레이어와 같이). LayerName enum: SKY(하늘), FAR(원경), MID(중경), PLAY(플레이), FRONT(전경), BACK(배경), ImageKey 끝과 같음(10/29 영어로 변경).</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -606,7 +606,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>하늘</t>
+          <t>SKY</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>원경</t>
+          <t>FAR</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>중경</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>플레이</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>전경</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>하늘</t>
+          <t>SKY</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>원경</t>
+          <t>FAR</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>중경</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>플레이</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>하늘</t>
+          <t>SKY</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>원경</t>
+          <t>FAR</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>중경</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>플레이</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>배경</t>
+          <t>BACK</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>플레이</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
